--- a/KatalonData/IVT/IVT_Login.xlsx
+++ b/KatalonData/IVT/IVT_Login.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\IVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5109B6-8D0B-4272-9CFF-8E0016F30D74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BC0387-6D1A-448D-A767-3DD89AA51E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Submit_SameJson" sheetId="2" r:id="rId1"/>
-    <sheet name="Submit_ChangedJson" sheetId="1" r:id="rId2"/>
+    <sheet name="Submit_SameJson" sheetId="6" r:id="rId1"/>
+    <sheet name="Submit_ChangedAppId" sheetId="3" r:id="rId2"/>
+    <sheet name="Submit_ChangedParcel" sheetId="1" r:id="rId3"/>
+    <sheet name="Submit_ChangedAddress" sheetId="4" r:id="rId4"/>
+    <sheet name="Submit_ChangedCustom" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="16">
   <si>
     <t>Result</t>
   </si>
@@ -61,11 +64,6 @@
   </si>
   <si>
     <t>JSONBody</t>
-  </si>
-  <si>
-    <t>Submit Request:
-applicationId- will always be 975.
-remittanceId- will always be unique(alphanumeric).</t>
   </si>
   <si>
     <t>{
@@ -112,11 +110,140 @@
   <si>
     <t>Thu May 28 18:18:00 IST 2026</t>
   </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "123456",
+  "applicationId": "1023",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "123456",
+  "applicationId": "1025",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Submit Request:
+applicationId- will always be 1024.
+remittanceId- will always be unique(alphanumeric).</t>
+  </si>
+  <si>
+    <t>{
+  "amount": 20.00,
+  "clientAccountNumber": "123456",
+  "applicationId": "1024",
+  "remittanceId": "ABC12329",
+  "cashierName": "Cashier1",
+  "pinpadName": "Counter-001",
+  "parcel": [
+    ["1", "2", "4"],
+    ["1", "2", "3"],
+    ["1", "2", "3"]
+  ],
+  "billingAddress": {
+    "firstName": "Jane",
+    "lastName": "Doe",
+    "companyName": "ABC Company",
+    "address": "123 Main St",
+    "address2": "Apt 5",
+    "postalCode": "22201",
+    "city": "Arlington",
+    "state": "VA",
+    "country": "USA",
+    "phone": "111-222-3333",
+    "email": "jane@email.com"
+  },
+  "customData": {
+    "user_defined_1": "value 1",
+    "user_defined_2": "value 2",
+    "user_defined_3": "value 3",
+    "user_defined_4": "value 4",
+    "user_defined_5": "value 5",
+    "user_defined_6": "value 6",
+    "user_defined_7": "value 7",
+    "user_defined_8": "value 8",
+    "user_defined_9": "value 9",
+    "user_defined_10": "value 10"
+  }
+}</t>
+  </si>
+  <si>
+    <t>Mon Sep 07 23:44:39 IST 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -191,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -213,6 +340,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,17 +677,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62AF84F9-04C5-40A5-B305-5AA20B298F7A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7BCB95-1CAD-42FE-8648-5B8C205E818D}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.90625" style="4" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="16.7265625" style="7" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="47.7265625" style="5" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.90625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.7265625" style="4" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="40.54296875" style="4" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="8.7265625" style="4" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="25.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -581,14 +711,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>4</v>
@@ -597,7 +727,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -627,17 +757,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4237FBEF-0E43-4D7C-A492-096F026631EA}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.90625" style="4" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="16.7265625" style="7" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="47.7265625" style="5" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.90625" style="4" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="13.7265625" style="4" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="40.54296875" style="4" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="8.7265625" style="4" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="7" width="23.54296875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -661,15 +791,9 @@
       </c>
     </row>
     <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A2" s="4"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="5"/>
       <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
@@ -677,7 +801,94 @@
         <v>6</v>
       </c>
       <c r="F2" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="16.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -705,4 +916,160 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825776FB-CEF4-435E-8470-EFDD60A698DF}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="16.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2BBE81-9849-406E-A59D-BAB233FD5CD1}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" style="4" width="6.90625" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="7" width="16.7265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="5" width="47.7265625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="4" width="7.90625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="4" width="13.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="4" width="40.54296875" collapsed="true"/>
+    <col min="7" max="16384" style="4" width="8.7265625" collapsed="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="3" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>